--- a/tests/fixtures/tne_planted/data/Booking_Detail_Report.xlsx
+++ b/tests/fixtures/tne_planted/data/Booking_Detail_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="61">
   <si>
     <t>Lead Traveller Name</t>
   </si>
@@ -37,40 +37,40 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>Costa, Bruno</t>
+    <t>Dubois, Camille</t>
   </si>
   <si>
     <t>Larsen, Freya</t>
   </si>
   <si>
+    <t>Osei, Kwame</t>
+  </si>
+  <si>
+    <t>Fischer, Lena</t>
+  </si>
+  <si>
+    <t>Patel, Nisha</t>
+  </si>
+  <si>
     <t>Ibrahim, Yusuf</t>
+  </si>
+  <si>
+    <t>Wong, Kelly</t>
+  </si>
+  <si>
+    <t>Costa, Bruno</t>
+  </si>
+  <si>
+    <t>Haddad, Omar</t>
+  </si>
+  <si>
+    <t>Alvarez, Diego</t>
   </si>
   <si>
     <t>Singh, Manpreet</t>
   </si>
   <si>
-    <t>Haddad, Omar</t>
-  </si>
-  <si>
-    <t>Fischer, Lena</t>
-  </si>
-  <si>
-    <t>Wong, Kelly</t>
-  </si>
-  <si>
-    <t>Osei, Kwame</t>
-  </si>
-  <si>
-    <t>Dubois, Camille</t>
-  </si>
-  <si>
-    <t>Patel, Nisha</t>
-  </si>
-  <si>
     <t>Novak, Petra</t>
-  </si>
-  <si>
-    <t>Alvarez, Diego</t>
   </si>
   <si>
     <t>Nakamura, Yuki</t>
@@ -85,13 +85,13 @@
     <t>Okonkwo, Emeka</t>
   </si>
   <si>
+    <t>Domestic</t>
+  </si>
+  <si>
     <t>International</t>
   </si>
   <si>
     <t>Trans Tasman</t>
-  </si>
-  <si>
-    <t>Domestic</t>
   </si>
   <si>
     <t>Booked</t>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
   </si>
   <si>
     <t>AUD</t>
@@ -529,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G281"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -566,16 +569,16 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1">
-        <v>46105</v>
+        <v>45736</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -589,16 +592,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1">
-        <v>46035</v>
+        <v>45933</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -609,111 +612,111 @@
         <v>700002</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1">
-        <v>45774</v>
+        <v>45797</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>700003</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
       <c r="F5" s="1">
-        <v>45876</v>
+        <v>45997</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>700004</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
-        <v>46032</v>
+        <v>45943</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>700005</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1">
-        <v>45672</v>
+        <v>45693</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>700006</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="1">
-        <v>45763</v>
+        <v>45765</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -727,21 +730,21 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
-        <v>45930</v>
+        <v>45687</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>700008</v>
@@ -750,21 +753,21 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="1">
-        <v>46117</v>
+        <v>45978</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>700009</v>
@@ -773,21 +776,21 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>700010</v>
@@ -796,21 +799,21 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1">
-        <v>45717</v>
+        <v>45856</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>700011</v>
@@ -819,136 +822,136 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1">
-        <v>45981</v>
+        <v>45838</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>700012</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1">
-        <v>45876</v>
+        <v>46131</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>700013</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1">
-        <v>46005</v>
+        <v>45885</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>700014</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1">
-        <v>46136</v>
+        <v>45961</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>700015</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1">
-        <v>45916</v>
+        <v>45911</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>700016</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1">
-        <v>46068</v>
+        <v>46060</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>700017</v>
@@ -957,67 +960,67 @@
         <v>24</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1">
-        <v>45937</v>
+        <v>45927</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>700018</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1">
-        <v>46068</v>
+        <v>45865</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>700019</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="1">
-        <v>45727</v>
+        <v>46052</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22">
         <v>700020</v>
@@ -1026,39 +1029,39 @@
         <v>24</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="1">
-        <v>45732</v>
+        <v>45966</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>700021</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1">
-        <v>46016</v>
+        <v>45760</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1069,47 +1072,47 @@
         <v>700022</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F24" s="1">
-        <v>45987</v>
+        <v>45790</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>700023</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1">
-        <v>46007</v>
+        <v>45911</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>700024</v>
@@ -1118,21 +1121,21 @@
         <v>23</v>
       </c>
       <c r="D26">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="1">
-        <v>46043</v>
+        <v>45723</v>
       </c>
       <c r="G26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27">
         <v>700025</v>
@@ -1141,67 +1144,67 @@
         <v>24</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F27" s="1">
-        <v>45730</v>
+        <v>45776</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B28">
         <v>700026</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F28" s="1">
-        <v>45798</v>
+        <v>45759</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>700027</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1">
-        <v>45776</v>
+        <v>46134</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B30">
         <v>700028</v>
@@ -1210,21 +1213,21 @@
         <v>25</v>
       </c>
       <c r="D30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1">
-        <v>45886</v>
+        <v>46029</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B31">
         <v>700029</v>
@@ -1233,21 +1236,21 @@
         <v>23</v>
       </c>
       <c r="D31">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="1">
-        <v>45676</v>
+        <v>45819</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>700030</v>
@@ -1256,21 +1259,21 @@
         <v>25</v>
       </c>
       <c r="D32">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1">
-        <v>46008</v>
+        <v>45796</v>
       </c>
       <c r="G32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>700031</v>
@@ -1279,108 +1282,108 @@
         <v>25</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="1">
-        <v>46057</v>
+        <v>46012</v>
       </c>
       <c r="G33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>700032</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D34">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F34" s="1">
-        <v>45681</v>
+        <v>45707</v>
       </c>
       <c r="G34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>700033</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F35" s="1">
-        <v>45732</v>
+        <v>45662</v>
       </c>
       <c r="G35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B36">
         <v>700034</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D36">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
       </c>
       <c r="F36" s="1">
-        <v>45845</v>
+        <v>45976</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B37">
         <v>700035</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D37">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="1">
-        <v>45762</v>
+        <v>45898</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1391,47 +1394,47 @@
         <v>700036</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
       </c>
       <c r="F38" s="1">
-        <v>46069</v>
+        <v>45859</v>
       </c>
       <c r="G38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B39">
         <v>700037</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1">
-        <v>45896</v>
+        <v>45733</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>700038</v>
@@ -1440,154 +1443,154 @@
         <v>23</v>
       </c>
       <c r="D40">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="1">
-        <v>45944</v>
+        <v>45878</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B41">
         <v>700039</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F41" s="1">
-        <v>45836</v>
+        <v>46119</v>
       </c>
       <c r="G41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B42">
         <v>700040</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1">
-        <v>45894</v>
+        <v>45982</v>
       </c>
       <c r="G42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B43">
         <v>700041</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D43">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
       </c>
       <c r="F43" s="1">
-        <v>45706</v>
+        <v>46135</v>
       </c>
       <c r="G43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>700042</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="1">
-        <v>45825</v>
+        <v>45802</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B45">
         <v>700043</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="1">
-        <v>45763</v>
+        <v>45867</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B46">
         <v>700044</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="1">
-        <v>45832</v>
+        <v>45788</v>
       </c>
       <c r="G46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1601,16 +1604,16 @@
         <v>24</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1">
-        <v>46058</v>
+        <v>45738</v>
       </c>
       <c r="G47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1624,131 +1627,131 @@
         <v>23</v>
       </c>
       <c r="D48">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F48" s="1">
-        <v>45821</v>
+        <v>45871</v>
       </c>
       <c r="G48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B49">
         <v>700047</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1">
-        <v>45989</v>
+        <v>45752</v>
       </c>
       <c r="G49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B50">
         <v>700048</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1">
-        <v>45706</v>
+        <v>45994</v>
       </c>
       <c r="G50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B51">
         <v>700049</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D51">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
       </c>
       <c r="F51" s="1">
-        <v>46012</v>
+        <v>45745</v>
       </c>
       <c r="G51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B52">
         <v>700050</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
       </c>
       <c r="F52" s="1">
-        <v>45984</v>
+        <v>45968</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B53">
         <v>700051</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
       </c>
       <c r="F53" s="1">
-        <v>45820</v>
+        <v>45678</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1759,24 +1762,24 @@
         <v>700052</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D54">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
       </c>
       <c r="F54" s="1">
-        <v>46097</v>
+        <v>45705</v>
       </c>
       <c r="G54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B55">
         <v>700053</v>
@@ -1785,67 +1788,67 @@
         <v>24</v>
       </c>
       <c r="D55">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1">
-        <v>45975</v>
+        <v>46083</v>
       </c>
       <c r="G55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B56">
         <v>700054</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D56">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
         <v>26</v>
       </c>
       <c r="F56" s="1">
-        <v>45754</v>
+        <v>45938</v>
       </c>
       <c r="G56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B57">
         <v>700055</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
       </c>
       <c r="F57" s="1">
-        <v>45987</v>
+        <v>45830</v>
       </c>
       <c r="G57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B58">
         <v>700056</v>
@@ -1854,21 +1857,21 @@
         <v>23</v>
       </c>
       <c r="D58">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1">
-        <v>46099</v>
+        <v>46034</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B59">
         <v>700057</v>
@@ -1877,85 +1880,85 @@
         <v>23</v>
       </c>
       <c r="D59">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1">
-        <v>45750</v>
+        <v>45936</v>
       </c>
       <c r="G59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B60">
         <v>700058</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D60">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F60" s="1">
-        <v>45734</v>
+        <v>45975</v>
       </c>
       <c r="G60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B61">
         <v>700059</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D61">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1">
-        <v>46029</v>
+        <v>45684</v>
       </c>
       <c r="G61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>700060</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F62" s="1">
-        <v>46095</v>
+        <v>45762</v>
       </c>
       <c r="G62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1966,24 +1969,24 @@
         <v>700061</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
       </c>
       <c r="F63" s="1">
-        <v>45913</v>
+        <v>46083</v>
       </c>
       <c r="G63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B64">
         <v>700062</v>
@@ -1992,21 +1995,21 @@
         <v>24</v>
       </c>
       <c r="D64">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
       </c>
       <c r="F64" s="1">
-        <v>45796</v>
+        <v>45924</v>
       </c>
       <c r="G64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B65">
         <v>700063</v>
@@ -2015,62 +2018,62 @@
         <v>23</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
       </c>
       <c r="F65" s="1">
-        <v>45703</v>
+        <v>45817</v>
       </c>
       <c r="G65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B66">
         <v>700064</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1">
-        <v>45665</v>
+        <v>45761</v>
       </c>
       <c r="G66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B67">
         <v>700065</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
         <v>26</v>
       </c>
       <c r="F67" s="1">
-        <v>45704</v>
+        <v>45783</v>
       </c>
       <c r="G67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2081,24 +2084,24 @@
         <v>700066</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D68">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F68" s="1">
-        <v>45758</v>
+        <v>45710</v>
       </c>
       <c r="G68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B69">
         <v>700067</v>
@@ -2107,44 +2110,44 @@
         <v>25</v>
       </c>
       <c r="D69">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
       </c>
       <c r="F69" s="1">
-        <v>45855</v>
+        <v>46011</v>
       </c>
       <c r="G69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B70">
         <v>700068</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E70" t="s">
         <v>26</v>
       </c>
       <c r="F70" s="1">
-        <v>45845</v>
+        <v>45770</v>
       </c>
       <c r="G70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B71">
         <v>700069</v>
@@ -2153,67 +2156,67 @@
         <v>24</v>
       </c>
       <c r="D71">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1">
-        <v>45663</v>
+        <v>46133</v>
       </c>
       <c r="G71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72">
         <v>700070</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
         <v>27</v>
       </c>
-      <c r="E72" t="s">
-        <v>28</v>
-      </c>
       <c r="F72" s="1">
-        <v>45826</v>
+        <v>46066</v>
       </c>
       <c r="G72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B73">
         <v>700071</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D73">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1">
-        <v>45753</v>
+        <v>46012</v>
       </c>
       <c r="G73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B74">
         <v>700072</v>
@@ -2222,62 +2225,62 @@
         <v>25</v>
       </c>
       <c r="D74">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F74" s="1">
-        <v>46089</v>
+        <v>45925</v>
       </c>
       <c r="G74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B75">
         <v>700073</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F75" s="1">
-        <v>45940</v>
+        <v>45760</v>
       </c>
       <c r="G75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B76">
         <v>700074</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
       </c>
       <c r="F76" s="1">
-        <v>45809</v>
+        <v>45803</v>
       </c>
       <c r="G76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2288,24 +2291,24 @@
         <v>700075</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D77">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
       </c>
       <c r="F77" s="1">
-        <v>45712</v>
+        <v>45717</v>
       </c>
       <c r="G77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B78">
         <v>700076</v>
@@ -2314,21 +2317,21 @@
         <v>25</v>
       </c>
       <c r="D78">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
       </c>
       <c r="F78" s="1">
-        <v>45789</v>
+        <v>45712</v>
       </c>
       <c r="G78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B79">
         <v>700077</v>
@@ -2337,21 +2340,21 @@
         <v>25</v>
       </c>
       <c r="D79">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
       </c>
       <c r="F79" s="1">
-        <v>45753</v>
+        <v>46033</v>
       </c>
       <c r="G79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B80">
         <v>700078</v>
@@ -2360,21 +2363,21 @@
         <v>24</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E80" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F80" s="1">
-        <v>45740</v>
+        <v>46127</v>
       </c>
       <c r="G80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B81">
         <v>700079</v>
@@ -2383,16 +2386,16 @@
         <v>24</v>
       </c>
       <c r="D81">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F81" s="1">
-        <v>46121</v>
+        <v>46018</v>
       </c>
       <c r="G81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2403,111 +2406,111 @@
         <v>700080</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D82">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E82" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1">
-        <v>46091</v>
+        <v>46034</v>
       </c>
       <c r="G82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B83">
         <v>700081</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D83">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="G83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84">
         <v>700082</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D84">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1">
-        <v>45809</v>
+        <v>46042</v>
       </c>
       <c r="G84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B85">
         <v>700083</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D85">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="E85" t="s">
         <v>26</v>
       </c>
       <c r="F85" s="1">
-        <v>45819</v>
+        <v>46032</v>
       </c>
       <c r="G85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B86">
         <v>700084</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D86">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
       </c>
       <c r="F86" s="1">
-        <v>45721</v>
+        <v>45841</v>
       </c>
       <c r="G86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2518,24 +2521,24 @@
         <v>700085</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F87" s="1">
-        <v>46036</v>
+        <v>45844</v>
       </c>
       <c r="G87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B88">
         <v>700086</v>
@@ -2544,274 +2547,274 @@
         <v>23</v>
       </c>
       <c r="D88">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F88" s="1">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="G88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B89">
         <v>700087</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F89" s="1">
-        <v>45721</v>
+        <v>45834</v>
       </c>
       <c r="G89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B90">
         <v>700088</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D90">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F90" s="1">
-        <v>46115</v>
+        <v>45885</v>
       </c>
       <c r="G90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B91">
         <v>700089</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F91" s="1">
-        <v>45932</v>
+        <v>45861</v>
       </c>
       <c r="G91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B92">
         <v>700090</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E92" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1">
-        <v>45905</v>
+        <v>45927</v>
       </c>
       <c r="G92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B93">
         <v>700091</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D93">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1">
-        <v>46052</v>
+        <v>45986</v>
       </c>
       <c r="G93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B94">
         <v>700092</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D94">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F94" s="1">
-        <v>45734</v>
+        <v>46052</v>
       </c>
       <c r="G94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B95">
         <v>700093</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D95">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E95" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F95" s="1">
-        <v>45922</v>
+        <v>45986</v>
       </c>
       <c r="G95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B96">
         <v>700094</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D96">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F96" s="1">
-        <v>46117</v>
+        <v>46061</v>
       </c>
       <c r="G96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B97">
         <v>700095</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F97" s="1">
-        <v>46091</v>
+        <v>45765</v>
       </c>
       <c r="G97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B98">
         <v>700096</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D98">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
       </c>
       <c r="F98" s="1">
-        <v>46128</v>
+        <v>45863</v>
       </c>
       <c r="G98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B99">
         <v>700097</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D99">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1">
-        <v>46111</v>
+        <v>45889</v>
       </c>
       <c r="G99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B100">
         <v>700098</v>
@@ -2820,113 +2823,113 @@
         <v>24</v>
       </c>
       <c r="D100">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F100" s="1">
-        <v>45970</v>
+        <v>46107</v>
       </c>
       <c r="G100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B101">
         <v>700099</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D101">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E101" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1">
-        <v>45767</v>
+        <v>46100</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B102">
         <v>700100</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D102">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E102" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F102" s="1">
-        <v>45755</v>
+        <v>45951</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B103">
         <v>700101</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D103">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E103" t="s">
         <v>26</v>
       </c>
       <c r="F103" s="1">
-        <v>46114</v>
+        <v>45720</v>
       </c>
       <c r="G103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B104">
         <v>700102</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D104">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
       </c>
       <c r="F104" s="1">
-        <v>45915</v>
+        <v>45767</v>
       </c>
       <c r="G104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B105">
         <v>700103</v>
@@ -2935,39 +2938,39 @@
         <v>23</v>
       </c>
       <c r="D105">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
       </c>
       <c r="F105" s="1">
-        <v>45771</v>
+        <v>45920</v>
       </c>
       <c r="G105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B106">
         <v>700104</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D106">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E106" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="G106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -2978,47 +2981,47 @@
         <v>700105</v>
       </c>
       <c r="C107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D107">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>26</v>
       </c>
       <c r="F107" s="1">
-        <v>45686</v>
+        <v>45800</v>
       </c>
       <c r="G107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B108">
         <v>700106</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D108">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="E108" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F108" s="1">
-        <v>45927</v>
+        <v>45946</v>
       </c>
       <c r="G108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B109">
         <v>700107</v>
@@ -3027,159 +3030,159 @@
         <v>23</v>
       </c>
       <c r="D109">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F109" s="1">
-        <v>45693</v>
+        <v>46043</v>
       </c>
       <c r="G109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B110">
         <v>700108</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110">
+        <v>22</v>
+      </c>
+      <c r="E110" t="s">
         <v>27</v>
       </c>
-      <c r="E110" t="s">
-        <v>26</v>
-      </c>
       <c r="F110" s="1">
-        <v>46084</v>
+        <v>45955</v>
       </c>
       <c r="G110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B111">
         <v>700109</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D111">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
       </c>
       <c r="F111" s="1">
-        <v>45948</v>
+        <v>46022</v>
       </c>
       <c r="G111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B112">
         <v>700110</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D112">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
       </c>
       <c r="F112" s="1">
-        <v>46011</v>
+        <v>45847</v>
       </c>
       <c r="G112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B113">
         <v>700111</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1">
-        <v>46106</v>
+        <v>45660</v>
       </c>
       <c r="G113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B114">
         <v>700112</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D114">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1">
-        <v>45787</v>
+        <v>46114</v>
       </c>
       <c r="G114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B115">
         <v>700113</v>
       </c>
       <c r="C115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D115">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
       </c>
       <c r="F115" s="1">
-        <v>45959</v>
+        <v>45934</v>
       </c>
       <c r="G115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B116">
         <v>700114</v>
@@ -3188,21 +3191,21 @@
         <v>25</v>
       </c>
       <c r="D116">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F116" s="1">
-        <v>45901</v>
+        <v>45751</v>
       </c>
       <c r="G116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B117">
         <v>700115</v>
@@ -3211,136 +3214,136 @@
         <v>25</v>
       </c>
       <c r="D117">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
       </c>
       <c r="F117" s="1">
-        <v>45728</v>
+        <v>45846</v>
       </c>
       <c r="G117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B118">
         <v>700116</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D118">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F118" s="1">
-        <v>45833</v>
+        <v>45994</v>
       </c>
       <c r="G118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B119">
         <v>700117</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1">
-        <v>45821</v>
+        <v>46065</v>
       </c>
       <c r="G119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B120">
         <v>700118</v>
       </c>
       <c r="C120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D120">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F120" s="1">
-        <v>45696</v>
+        <v>45754</v>
       </c>
       <c r="G120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B121">
         <v>700119</v>
       </c>
       <c r="C121" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D121">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E121" t="s">
         <v>26</v>
       </c>
       <c r="F121" s="1">
-        <v>46096</v>
+        <v>46047</v>
       </c>
       <c r="G121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B122">
         <v>700120</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D122">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E122" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1">
-        <v>45898</v>
+        <v>46056</v>
       </c>
       <c r="G122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B123">
         <v>700121</v>
@@ -3349,16 +3352,16 @@
         <v>24</v>
       </c>
       <c r="D123">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1">
-        <v>45804</v>
+        <v>45786</v>
       </c>
       <c r="G123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3369,47 +3372,47 @@
         <v>700122</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D124">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1">
-        <v>45728</v>
+        <v>46014</v>
       </c>
       <c r="G124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125">
         <v>700123</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D125">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
       </c>
       <c r="F125" s="1">
-        <v>45889</v>
+        <v>46111</v>
       </c>
       <c r="G125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B126">
         <v>700124</v>
@@ -3418,21 +3421,21 @@
         <v>23</v>
       </c>
       <c r="D126">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E126" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F126" s="1">
-        <v>45798</v>
+        <v>45862</v>
       </c>
       <c r="G126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B127">
         <v>700125</v>
@@ -3441,62 +3444,62 @@
         <v>24</v>
       </c>
       <c r="D127">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E127" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F127" s="1">
-        <v>45700</v>
+        <v>46142</v>
       </c>
       <c r="G127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B128">
         <v>700126</v>
       </c>
       <c r="C128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D128">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E128" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1">
-        <v>46127</v>
+        <v>45704</v>
       </c>
       <c r="G128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B129">
         <v>700127</v>
       </c>
       <c r="C129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D129">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
       </c>
       <c r="F129" s="1">
-        <v>46115</v>
+        <v>45679</v>
       </c>
       <c r="G129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3507,24 +3510,24 @@
         <v>700128</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D130">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F130" s="1">
-        <v>45909</v>
+        <v>45933</v>
       </c>
       <c r="G130" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B131">
         <v>700129</v>
@@ -3533,21 +3536,21 @@
         <v>23</v>
       </c>
       <c r="D131">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
       </c>
       <c r="F131" s="1">
-        <v>45964</v>
+        <v>45690</v>
       </c>
       <c r="G131" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B132">
         <v>700130</v>
@@ -3556,67 +3559,67 @@
         <v>23</v>
       </c>
       <c r="D132">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E132" t="s">
         <v>26</v>
       </c>
       <c r="F132" s="1">
-        <v>45831</v>
+        <v>45807</v>
       </c>
       <c r="G132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B133">
         <v>700131</v>
       </c>
       <c r="C133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D133">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E133" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F133" s="1">
-        <v>46076</v>
+        <v>45940</v>
       </c>
       <c r="G133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B134">
         <v>700132</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D134">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E134" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F134" s="1">
-        <v>45766</v>
+        <v>46018</v>
       </c>
       <c r="G134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B135">
         <v>700133</v>
@@ -3625,21 +3628,21 @@
         <v>24</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
       </c>
       <c r="F135" s="1">
-        <v>45747</v>
+        <v>45871</v>
       </c>
       <c r="G135" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B136">
         <v>700134</v>
@@ -3648,67 +3651,67 @@
         <v>25</v>
       </c>
       <c r="D136">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="E136" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F136" s="1">
-        <v>45875</v>
+        <v>45674</v>
       </c>
       <c r="G136" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B137">
         <v>700135</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D137">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F137" s="1">
-        <v>45822</v>
+        <v>46065</v>
       </c>
       <c r="G137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B138">
         <v>700136</v>
       </c>
       <c r="C138" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D138">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E138" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F138" s="1">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="G138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B139">
         <v>700137</v>
@@ -3717,21 +3720,21 @@
         <v>25</v>
       </c>
       <c r="D139">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
       </c>
       <c r="F139" s="1">
-        <v>45678</v>
+        <v>45884</v>
       </c>
       <c r="G139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B140">
         <v>700138</v>
@@ -3740,21 +3743,21 @@
         <v>24</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F140" s="1">
-        <v>45891</v>
+        <v>45994</v>
       </c>
       <c r="G140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B141">
         <v>700139</v>
@@ -3763,21 +3766,21 @@
         <v>23</v>
       </c>
       <c r="D141">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E141" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F141" s="1">
-        <v>45662</v>
+        <v>45875</v>
       </c>
       <c r="G141" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B142">
         <v>700140</v>
@@ -3786,343 +3789,343 @@
         <v>25</v>
       </c>
       <c r="D142">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1">
-        <v>46046</v>
+        <v>45737</v>
       </c>
       <c r="G142" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B143">
         <v>700141</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D143">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F143" s="1">
-        <v>45929</v>
+        <v>45999</v>
       </c>
       <c r="G143" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B144">
         <v>700142</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D144">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F144" s="1">
-        <v>45779</v>
+        <v>46026</v>
       </c>
       <c r="G144" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B145">
         <v>700143</v>
       </c>
       <c r="C145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E145" t="s">
         <v>26</v>
       </c>
       <c r="F145" s="1">
-        <v>45949</v>
+        <v>45869</v>
       </c>
       <c r="G145" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B146">
         <v>700144</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D146">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E146" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F146" s="1">
-        <v>46022</v>
+        <v>45798</v>
       </c>
       <c r="G146" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B147">
         <v>700145</v>
       </c>
       <c r="C147" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D147">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E147" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F147" s="1">
-        <v>45964</v>
+        <v>45863</v>
       </c>
       <c r="G147" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B148">
         <v>700146</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D148">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E148" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F148" s="1">
-        <v>45715</v>
+        <v>46130</v>
       </c>
       <c r="G148" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B149">
         <v>700147</v>
       </c>
       <c r="C149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D149">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
       </c>
       <c r="F149" s="1">
-        <v>45868</v>
+        <v>45941</v>
       </c>
       <c r="G149" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B150">
         <v>700148</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D150">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
       </c>
       <c r="F150" s="1">
-        <v>45904</v>
+        <v>45998</v>
       </c>
       <c r="G150" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B151">
         <v>700149</v>
       </c>
       <c r="C151" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D151">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E151" t="s">
         <v>26</v>
       </c>
       <c r="F151" s="1">
-        <v>45880</v>
+        <v>46093</v>
       </c>
       <c r="G151" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B152">
         <v>700150</v>
       </c>
       <c r="C152" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D152">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E152" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F152" s="1">
-        <v>45687</v>
+        <v>45789</v>
       </c>
       <c r="G152" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B153">
         <v>700151</v>
       </c>
       <c r="C153" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D153">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1">
-        <v>45831</v>
+        <v>46014</v>
       </c>
       <c r="G153" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B154">
         <v>700152</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D154">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
       </c>
       <c r="F154" s="1">
-        <v>45829</v>
+        <v>45921</v>
       </c>
       <c r="G154" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B155">
         <v>700153</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
       </c>
       <c r="F155" s="1">
-        <v>46105</v>
+        <v>45952</v>
       </c>
       <c r="G155" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B156">
         <v>700154</v>
       </c>
       <c r="C156" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D156">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F156" s="1">
-        <v>46124</v>
+        <v>45938</v>
       </c>
       <c r="G156" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B157">
         <v>700155</v>
@@ -4131,21 +4134,21 @@
         <v>23</v>
       </c>
       <c r="D157">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E157" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F157" s="1">
-        <v>45725</v>
+        <v>45690</v>
       </c>
       <c r="G157" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B158">
         <v>700156</v>
@@ -4154,90 +4157,90 @@
         <v>23</v>
       </c>
       <c r="D158">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F158" s="1">
-        <v>45691</v>
+        <v>45726</v>
       </c>
       <c r="G158" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B159">
         <v>700157</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D159">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
       </c>
       <c r="F159" s="1">
-        <v>45851</v>
+        <v>45751</v>
       </c>
       <c r="G159" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B160">
         <v>700158</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D160">
+        <v>49</v>
+      </c>
+      <c r="E160" t="s">
         <v>27</v>
       </c>
-      <c r="E160" t="s">
-        <v>26</v>
-      </c>
       <c r="F160" s="1">
-        <v>45964</v>
+        <v>45777</v>
       </c>
       <c r="G160" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B161">
         <v>700159</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D161">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
       </c>
       <c r="F161" s="1">
-        <v>46134</v>
+        <v>46026</v>
       </c>
       <c r="G161" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B162">
         <v>700160</v>
@@ -4246,44 +4249,44 @@
         <v>25</v>
       </c>
       <c r="D162">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="1">
-        <v>46072</v>
+        <v>45942</v>
       </c>
       <c r="G162" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B163">
         <v>700161</v>
       </c>
       <c r="C163" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D163">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F163" s="1">
-        <v>45864</v>
+        <v>46020</v>
       </c>
       <c r="G163" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B164">
         <v>700162</v>
@@ -4292,67 +4295,67 @@
         <v>25</v>
       </c>
       <c r="D164">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F164" s="1">
-        <v>45830</v>
+        <v>45889</v>
       </c>
       <c r="G164" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B165">
         <v>700163</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D165">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F165" s="1">
-        <v>46127</v>
+        <v>45777</v>
       </c>
       <c r="G165" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B166">
         <v>700164</v>
       </c>
       <c r="C166" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D166">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
       </c>
       <c r="F166" s="1">
-        <v>45747</v>
+        <v>46015</v>
       </c>
       <c r="G166" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B167">
         <v>700165</v>
@@ -4361,62 +4364,62 @@
         <v>23</v>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E167" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F167" s="1">
-        <v>45663</v>
+        <v>45702</v>
       </c>
       <c r="G167" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B168">
         <v>700166</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D168">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E168" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F168" s="1">
-        <v>45958</v>
+        <v>45934</v>
       </c>
       <c r="G168" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B169">
         <v>700167</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
       </c>
       <c r="F169" s="1">
-        <v>45748</v>
+        <v>46021</v>
       </c>
       <c r="G169" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4430,44 +4433,44 @@
         <v>24</v>
       </c>
       <c r="D170">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E170" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F170" s="1">
-        <v>46129</v>
+        <v>45899</v>
       </c>
       <c r="G170" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B171">
         <v>700169</v>
       </c>
       <c r="C171" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D171">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E171" t="s">
         <v>26</v>
       </c>
       <c r="F171" s="1">
-        <v>46092</v>
+        <v>45878</v>
       </c>
       <c r="G171" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B172">
         <v>700170</v>
@@ -4476,67 +4479,67 @@
         <v>24</v>
       </c>
       <c r="D172">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E172" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F172" s="1">
-        <v>45768</v>
+        <v>45806</v>
       </c>
       <c r="G172" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B173">
         <v>700171</v>
       </c>
       <c r="C173" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D173">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
         <v>26</v>
       </c>
       <c r="F173" s="1">
-        <v>46069</v>
+        <v>45865</v>
       </c>
       <c r="G173" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B174">
         <v>700172</v>
       </c>
       <c r="C174" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D174">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F174" s="1">
-        <v>46089</v>
+        <v>46004</v>
       </c>
       <c r="G174" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B175">
         <v>700173</v>
@@ -4545,269 +4548,269 @@
         <v>24</v>
       </c>
       <c r="D175">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E175" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F175" s="1">
-        <v>45986</v>
+        <v>45968</v>
       </c>
       <c r="G175" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B176">
         <v>700174</v>
       </c>
       <c r="C176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D176">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
       </c>
       <c r="F176" s="1">
-        <v>45992</v>
+        <v>45697</v>
       </c>
       <c r="G176" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B177">
         <v>700175</v>
       </c>
       <c r="C177" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D177">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E177" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F177" s="1">
-        <v>45706</v>
+        <v>46109</v>
       </c>
       <c r="G177" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B178">
         <v>700176</v>
       </c>
       <c r="C178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D178">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
       </c>
       <c r="F178" s="1">
-        <v>45846</v>
+        <v>46121</v>
       </c>
       <c r="G178" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B179">
         <v>700177</v>
       </c>
       <c r="C179" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D179">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E179" t="s">
         <v>26</v>
       </c>
       <c r="F179" s="1">
-        <v>45719</v>
+        <v>46035</v>
       </c>
       <c r="G179" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180">
         <v>700178</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D180">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F180" s="1">
-        <v>46070</v>
+        <v>45674</v>
       </c>
       <c r="G180" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B181">
         <v>700179</v>
       </c>
       <c r="C181" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D181">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
       </c>
       <c r="F181" s="1">
-        <v>45689</v>
+        <v>45997</v>
       </c>
       <c r="G181" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B182">
         <v>700180</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D182">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
       </c>
       <c r="F182" s="1">
-        <v>45744</v>
+        <v>45800</v>
       </c>
       <c r="G182" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B183">
         <v>700181</v>
       </c>
       <c r="C183" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D183">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
       </c>
       <c r="F183" s="1">
-        <v>46118</v>
+        <v>45740</v>
       </c>
       <c r="G183" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B184">
         <v>700182</v>
       </c>
       <c r="C184" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D184">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
       </c>
       <c r="F184" s="1">
-        <v>45675</v>
+        <v>46042</v>
       </c>
       <c r="G184" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B185">
         <v>700183</v>
       </c>
       <c r="C185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D185">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E185" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F185" s="1">
-        <v>45740</v>
+        <v>46059</v>
       </c>
       <c r="G185" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B186">
         <v>700184</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D186">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E186" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F186" s="1">
-        <v>46089</v>
+        <v>46075</v>
       </c>
       <c r="G186" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4821,21 +4824,21 @@
         <v>23</v>
       </c>
       <c r="D187">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E187" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F187" s="1">
-        <v>45981</v>
+        <v>45885</v>
       </c>
       <c r="G187" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B188">
         <v>700186</v>
@@ -4844,44 +4847,44 @@
         <v>24</v>
       </c>
       <c r="D188">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E188" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F188" s="1">
-        <v>45852</v>
+        <v>45708</v>
       </c>
       <c r="G188" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B189">
         <v>700187</v>
       </c>
       <c r="C189" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D189">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E189" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F189" s="1">
-        <v>46058</v>
+        <v>45973</v>
       </c>
       <c r="G189" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B190">
         <v>700188</v>
@@ -4890,21 +4893,21 @@
         <v>24</v>
       </c>
       <c r="D190">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E190" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F190" s="1">
-        <v>45895</v>
+        <v>45667</v>
       </c>
       <c r="G190" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B191">
         <v>700189</v>
@@ -4913,16 +4916,16 @@
         <v>23</v>
       </c>
       <c r="D191">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
       </c>
       <c r="F191" s="1">
-        <v>45879</v>
+        <v>45877</v>
       </c>
       <c r="G191" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -4933,47 +4936,47 @@
         <v>700190</v>
       </c>
       <c r="C192" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D192">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E192" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F192" s="1">
-        <v>46023</v>
+        <v>45711</v>
       </c>
       <c r="G192" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B193">
         <v>700191</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D193">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F193" s="1">
-        <v>46121</v>
+        <v>46065</v>
       </c>
       <c r="G193" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B194">
         <v>700192</v>
@@ -4982,39 +4985,39 @@
         <v>24</v>
       </c>
       <c r="D194">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E194" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F194" s="1">
-        <v>46135</v>
+        <v>45797</v>
       </c>
       <c r="G194" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B195">
         <v>700193</v>
       </c>
       <c r="C195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D195">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E195" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F195" s="1">
-        <v>46037</v>
+        <v>45705</v>
       </c>
       <c r="G195" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5025,93 +5028,93 @@
         <v>700194</v>
       </c>
       <c r="C196" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D196">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E196" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F196" s="1">
-        <v>45963</v>
+        <v>45846</v>
       </c>
       <c r="G196" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B197">
         <v>700195</v>
       </c>
       <c r="C197" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D197">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E197" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F197" s="1">
-        <v>45903</v>
+        <v>45818</v>
       </c>
       <c r="G197" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B198">
         <v>700196</v>
       </c>
       <c r="C198" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D198">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E198" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F198" s="1">
-        <v>45749</v>
+        <v>46089</v>
       </c>
       <c r="G198" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B199">
         <v>700197</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D199">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E199" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F199" s="1">
-        <v>46056</v>
+        <v>45943</v>
       </c>
       <c r="G199" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B200">
         <v>700198</v>
@@ -5120,159 +5123,159 @@
         <v>24</v>
       </c>
       <c r="D200">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E200" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F200" s="1">
-        <v>45944</v>
+        <v>46086</v>
       </c>
       <c r="G200" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B201">
         <v>700199</v>
       </c>
       <c r="C201" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D201">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E201" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F201" s="1">
-        <v>45920</v>
+        <v>45800</v>
       </c>
       <c r="G201" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B202">
         <v>700200</v>
       </c>
       <c r="C202" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D202">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E202" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F202" s="1">
-        <v>45865</v>
+        <v>45980</v>
       </c>
       <c r="G202" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B203">
         <v>700201</v>
       </c>
       <c r="C203" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D203">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E203" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F203" s="1">
-        <v>45790</v>
+        <v>46007</v>
       </c>
       <c r="G203" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B204">
         <v>700202</v>
       </c>
       <c r="C204" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D204">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F204" s="1">
-        <v>46013</v>
+        <v>46046</v>
       </c>
       <c r="G204" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B205">
         <v>700203</v>
       </c>
       <c r="C205" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D205">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>26</v>
       </c>
       <c r="F205" s="1">
-        <v>45753</v>
+        <v>45819</v>
       </c>
       <c r="G205" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B206">
         <v>700204</v>
       </c>
       <c r="C206" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D206">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E206" t="s">
         <v>26</v>
       </c>
       <c r="F206" s="1">
-        <v>46095</v>
+        <v>45721</v>
       </c>
       <c r="G206" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B207">
         <v>700205</v>
@@ -5281,228 +5284,228 @@
         <v>25</v>
       </c>
       <c r="D207">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E207" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F207" s="1">
-        <v>46049</v>
+        <v>45797</v>
       </c>
       <c r="G207" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B208">
         <v>700206</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D208">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E208" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F208" s="1">
-        <v>46063</v>
+        <v>45801</v>
       </c>
       <c r="G208" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B209">
         <v>700207</v>
       </c>
       <c r="C209" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D209">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E209" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F209" s="1">
-        <v>46081</v>
+        <v>45987</v>
       </c>
       <c r="G209" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B210">
         <v>700208</v>
       </c>
       <c r="C210" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D210">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E210" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F210" s="1">
-        <v>45966</v>
+        <v>45890</v>
       </c>
       <c r="G210" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B211">
         <v>700209</v>
       </c>
       <c r="C211" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D211">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E211" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F211" s="1">
-        <v>45888</v>
+        <v>45846</v>
       </c>
       <c r="G211" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B212">
         <v>700210</v>
       </c>
       <c r="C212" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D212">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F212" s="1">
-        <v>45805</v>
+        <v>46071</v>
       </c>
       <c r="G212" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B213">
         <v>700211</v>
       </c>
       <c r="C213" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D213">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E213" t="s">
         <v>26</v>
       </c>
       <c r="F213" s="1">
-        <v>45800</v>
+        <v>46064</v>
       </c>
       <c r="G213" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B214">
         <v>700212</v>
       </c>
       <c r="C214" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D214">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E214" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F214" s="1">
-        <v>45796</v>
+        <v>45954</v>
       </c>
       <c r="G214" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B215">
         <v>700213</v>
       </c>
       <c r="C215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D215">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E215" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F215" s="1">
-        <v>45862</v>
+        <v>45954</v>
       </c>
       <c r="G215" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B216">
         <v>700214</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D216">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E216" t="s">
         <v>26</v>
       </c>
       <c r="F216" s="1">
-        <v>45894</v>
+        <v>46054</v>
       </c>
       <c r="G216" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B217">
         <v>700215</v>
@@ -5511,44 +5514,44 @@
         <v>24</v>
       </c>
       <c r="D217">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E217" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F217" s="1">
-        <v>46009</v>
+        <v>45943</v>
       </c>
       <c r="G217" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B218">
         <v>700216</v>
       </c>
       <c r="C218" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D218">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
       </c>
       <c r="F218" s="1">
-        <v>45927</v>
+        <v>45839</v>
       </c>
       <c r="G218" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B219">
         <v>700217</v>
@@ -5557,16 +5560,16 @@
         <v>25</v>
       </c>
       <c r="D219">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
       </c>
       <c r="F219" s="1">
-        <v>45959</v>
+        <v>46054</v>
       </c>
       <c r="G219" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5580,39 +5583,39 @@
         <v>24</v>
       </c>
       <c r="D220">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E220" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F220" s="1">
-        <v>45717</v>
+        <v>45771</v>
       </c>
       <c r="G220" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B221">
         <v>700219</v>
       </c>
       <c r="C221" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D221">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E221" t="s">
         <v>26</v>
       </c>
       <c r="F221" s="1">
-        <v>45752</v>
+        <v>45860</v>
       </c>
       <c r="G221" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5623,7 +5626,7 @@
         <v>610001</v>
       </c>
       <c r="C222" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -5635,7 +5638,7 @@
         <v>29</v>
       </c>
       <c r="G222" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5646,7 +5649,7 @@
         <v>610003</v>
       </c>
       <c r="C223" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -5658,7 +5661,7 @@
         <v>30</v>
       </c>
       <c r="G223" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5669,7 +5672,7 @@
         <v>610005</v>
       </c>
       <c r="C224" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D224">
         <v>2</v>
@@ -5681,7 +5684,7 @@
         <v>31</v>
       </c>
       <c r="G224" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5692,7 +5695,7 @@
         <v>610007</v>
       </c>
       <c r="C225" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D225">
         <v>3</v>
@@ -5704,7 +5707,7 @@
         <v>32</v>
       </c>
       <c r="G225" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5715,7 +5718,7 @@
         <v>610009</v>
       </c>
       <c r="C226" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D226">
         <v>4</v>
@@ -5727,7 +5730,7 @@
         <v>33</v>
       </c>
       <c r="G226" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5738,7 +5741,7 @@
         <v>610011</v>
       </c>
       <c r="C227" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D227">
         <v>5</v>
@@ -5750,7 +5753,7 @@
         <v>34</v>
       </c>
       <c r="G227" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -5761,7 +5764,7 @@
         <v>610013</v>
       </c>
       <c r="C228" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D228">
         <v>6</v>
@@ -5773,7 +5776,7 @@
         <v>35</v>
       </c>
       <c r="G228" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -5784,7 +5787,7 @@
         <v>610015</v>
       </c>
       <c r="C229" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D229">
         <v>7</v>
@@ -5796,7 +5799,7 @@
         <v>36</v>
       </c>
       <c r="G229" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -5807,7 +5810,7 @@
         <v>610017</v>
       </c>
       <c r="C230" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D230">
         <v>8</v>
@@ -5819,7 +5822,7 @@
         <v>37</v>
       </c>
       <c r="G230" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -5830,7 +5833,7 @@
         <v>610019</v>
       </c>
       <c r="C231" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D231">
         <v>10</v>
@@ -5842,7 +5845,7 @@
         <v>38</v>
       </c>
       <c r="G231" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -5853,7 +5856,7 @@
         <v>610021</v>
       </c>
       <c r="C232" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D232">
         <v>14</v>
@@ -5865,7 +5868,7 @@
         <v>39</v>
       </c>
       <c r="G232" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -5876,7 +5879,7 @@
         <v>610023</v>
       </c>
       <c r="C233" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D233">
         <v>18</v>
@@ -5888,7 +5891,7 @@
         <v>40</v>
       </c>
       <c r="G233" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -5899,7 +5902,7 @@
         <v>610025</v>
       </c>
       <c r="C234" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D234">
         <v>25</v>
@@ -5911,7 +5914,7 @@
         <v>41</v>
       </c>
       <c r="G234" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -5922,7 +5925,7 @@
         <v>610027</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D235">
         <v>35</v>
@@ -5934,7 +5937,7 @@
         <v>42</v>
       </c>
       <c r="G235" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -5945,7 +5948,7 @@
         <v>610029</v>
       </c>
       <c r="C236" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D236">
         <v>60</v>
@@ -5957,7 +5960,7 @@
         <v>43</v>
       </c>
       <c r="G236" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -5968,7 +5971,7 @@
         <v>610030</v>
       </c>
       <c r="C237" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -5980,7 +5983,7 @@
         <v>44</v>
       </c>
       <c r="G237" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -5991,7 +5994,7 @@
         <v>610032</v>
       </c>
       <c r="C238" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -6003,7 +6006,7 @@
         <v>45</v>
       </c>
       <c r="G238" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6014,7 +6017,7 @@
         <v>610034</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -6026,7 +6029,7 @@
         <v>46</v>
       </c>
       <c r="G239" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6037,7 +6040,7 @@
         <v>610036</v>
       </c>
       <c r="C240" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -6049,7 +6052,7 @@
         <v>47</v>
       </c>
       <c r="G240" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6060,7 +6063,7 @@
         <v>610038</v>
       </c>
       <c r="C241" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D241">
         <v>3</v>
@@ -6072,7 +6075,7 @@
         <v>48</v>
       </c>
       <c r="G241" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6083,7 +6086,7 @@
         <v>610040</v>
       </c>
       <c r="C242" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D242">
         <v>7</v>
@@ -6095,7 +6098,7 @@
         <v>49</v>
       </c>
       <c r="G242" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6106,7 +6109,7 @@
         <v>610042</v>
       </c>
       <c r="C243" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D243">
         <v>11</v>
@@ -6118,7 +6121,7 @@
         <v>50</v>
       </c>
       <c r="G243" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6129,7 +6132,7 @@
         <v>610044</v>
       </c>
       <c r="C244" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D244">
         <v>13</v>
@@ -6141,7 +6144,7 @@
         <v>51</v>
       </c>
       <c r="G244" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6152,7 +6155,7 @@
         <v>610046</v>
       </c>
       <c r="C245" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D245">
         <v>14</v>
@@ -6164,7 +6167,7 @@
         <v>52</v>
       </c>
       <c r="G245" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6175,7 +6178,7 @@
         <v>610048</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D246">
         <v>16</v>
@@ -6187,7 +6190,7 @@
         <v>53</v>
       </c>
       <c r="G246" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6198,7 +6201,7 @@
         <v>610050</v>
       </c>
       <c r="C247" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D247">
         <v>20</v>
@@ -6210,7 +6213,7 @@
         <v>54</v>
       </c>
       <c r="G247" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6221,7 +6224,7 @@
         <v>610052</v>
       </c>
       <c r="C248" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D248">
         <v>25</v>
@@ -6233,7 +6236,7 @@
         <v>55</v>
       </c>
       <c r="G248" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6244,7 +6247,7 @@
         <v>610054</v>
       </c>
       <c r="C249" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D249">
         <v>30</v>
@@ -6256,7 +6259,7 @@
         <v>56</v>
       </c>
       <c r="G249" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6267,7 +6270,7 @@
         <v>610056</v>
       </c>
       <c r="C250" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D250">
         <v>40</v>
@@ -6279,7 +6282,7 @@
         <v>57</v>
       </c>
       <c r="G250" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6290,7 +6293,7 @@
         <v>610058</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D251">
         <v>50</v>
@@ -6302,7 +6305,7 @@
         <v>58</v>
       </c>
       <c r="G251" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6310,45 +6313,45 @@
         <v>21</v>
       </c>
       <c r="B252">
-        <v>610000</v>
+        <v>620001</v>
       </c>
       <c r="C252" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E252" t="s">
         <v>26</v>
       </c>
       <c r="F252" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G252" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B253">
-        <v>610002</v>
+        <v>620002</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E253" t="s">
         <v>26</v>
       </c>
       <c r="F253" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G253" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6356,22 +6359,22 @@
         <v>21</v>
       </c>
       <c r="B254">
-        <v>610004</v>
+        <v>610000</v>
       </c>
       <c r="C254" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D254">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E254" t="s">
         <v>26</v>
       </c>
       <c r="F254" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G254" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6379,22 +6382,22 @@
         <v>21</v>
       </c>
       <c r="B255">
-        <v>610006</v>
+        <v>610002</v>
       </c>
       <c r="C255" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
         <v>26</v>
       </c>
       <c r="F255" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G255" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6402,22 +6405,22 @@
         <v>21</v>
       </c>
       <c r="B256">
-        <v>610008</v>
+        <v>610004</v>
       </c>
       <c r="C256" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D256">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E256" t="s">
         <v>26</v>
       </c>
       <c r="F256" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G256" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6425,22 +6428,22 @@
         <v>21</v>
       </c>
       <c r="B257">
-        <v>610010</v>
+        <v>610006</v>
       </c>
       <c r="C257" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E257" t="s">
         <v>26</v>
       </c>
       <c r="F257" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G257" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -6448,22 +6451,22 @@
         <v>21</v>
       </c>
       <c r="B258">
-        <v>610012</v>
+        <v>610008</v>
       </c>
       <c r="C258" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E258" t="s">
         <v>26</v>
       </c>
       <c r="F258" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G258" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -6471,22 +6474,22 @@
         <v>21</v>
       </c>
       <c r="B259">
-        <v>610014</v>
+        <v>610010</v>
       </c>
       <c r="C259" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E259" t="s">
         <v>26</v>
       </c>
       <c r="F259" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G259" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -6494,22 +6497,22 @@
         <v>21</v>
       </c>
       <c r="B260">
-        <v>610016</v>
+        <v>610012</v>
       </c>
       <c r="C260" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D260">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E260" t="s">
         <v>26</v>
       </c>
       <c r="F260" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G260" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -6517,22 +6520,22 @@
         <v>21</v>
       </c>
       <c r="B261">
-        <v>610018</v>
+        <v>610014</v>
       </c>
       <c r="C261" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D261">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E261" t="s">
         <v>26</v>
       </c>
       <c r="F261" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G261" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -6540,22 +6543,22 @@
         <v>21</v>
       </c>
       <c r="B262">
-        <v>610020</v>
+        <v>610016</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D262">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E262" t="s">
         <v>26</v>
       </c>
       <c r="F262" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G262" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -6563,22 +6566,22 @@
         <v>21</v>
       </c>
       <c r="B263">
-        <v>610022</v>
+        <v>610018</v>
       </c>
       <c r="C263" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D263">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
         <v>26</v>
       </c>
       <c r="F263" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G263" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -6586,22 +6589,22 @@
         <v>21</v>
       </c>
       <c r="B264">
-        <v>610024</v>
+        <v>610020</v>
       </c>
       <c r="C264" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D264">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E264" t="s">
         <v>26</v>
       </c>
       <c r="F264" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G264" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -6609,22 +6612,22 @@
         <v>21</v>
       </c>
       <c r="B265">
-        <v>610026</v>
+        <v>610022</v>
       </c>
       <c r="C265" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D265">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E265" t="s">
         <v>26</v>
       </c>
       <c r="F265" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G265" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -6632,68 +6635,68 @@
         <v>21</v>
       </c>
       <c r="B266">
-        <v>610028</v>
+        <v>610024</v>
       </c>
       <c r="C266" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D266">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E266" t="s">
         <v>26</v>
       </c>
       <c r="F266" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G266" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B267">
-        <v>610031</v>
+        <v>610026</v>
       </c>
       <c r="C267" t="s">
         <v>23</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E267" t="s">
         <v>26</v>
       </c>
       <c r="F267" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="G267" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B268">
-        <v>610033</v>
+        <v>610028</v>
       </c>
       <c r="C268" t="s">
         <v>23</v>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E268" t="s">
         <v>26</v>
       </c>
       <c r="F268" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G268" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -6701,22 +6704,22 @@
         <v>22</v>
       </c>
       <c r="B269">
-        <v>610035</v>
+        <v>610031</v>
       </c>
       <c r="C269" t="s">
         <v>24</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E269" t="s">
         <v>26</v>
       </c>
       <c r="F269" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G269" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -6724,22 +6727,22 @@
         <v>22</v>
       </c>
       <c r="B270">
-        <v>610037</v>
+        <v>610033</v>
       </c>
       <c r="C270" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" t="s">
         <v>26</v>
       </c>
       <c r="F270" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G270" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -6747,22 +6750,22 @@
         <v>22</v>
       </c>
       <c r="B271">
-        <v>610039</v>
+        <v>610035</v>
       </c>
       <c r="C271" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D271">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E271" t="s">
         <v>26</v>
       </c>
       <c r="F271" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G271" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -6770,22 +6773,22 @@
         <v>22</v>
       </c>
       <c r="B272">
-        <v>610041</v>
+        <v>610037</v>
       </c>
       <c r="C272" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D272">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E272" t="s">
         <v>26</v>
       </c>
       <c r="F272" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G272" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -6793,22 +6796,22 @@
         <v>22</v>
       </c>
       <c r="B273">
-        <v>610043</v>
+        <v>610039</v>
       </c>
       <c r="C273" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D273">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E273" t="s">
         <v>26</v>
       </c>
       <c r="F273" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G273" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -6816,22 +6819,22 @@
         <v>22</v>
       </c>
       <c r="B274">
-        <v>610045</v>
+        <v>610041</v>
       </c>
       <c r="C274" t="s">
         <v>24</v>
       </c>
       <c r="D274">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>26</v>
       </c>
       <c r="F274" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G274" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -6839,22 +6842,22 @@
         <v>22</v>
       </c>
       <c r="B275">
-        <v>610047</v>
+        <v>610043</v>
       </c>
       <c r="C275" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D275">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E275" t="s">
         <v>26</v>
       </c>
       <c r="F275" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G275" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -6862,22 +6865,22 @@
         <v>22</v>
       </c>
       <c r="B276">
-        <v>610049</v>
+        <v>610045</v>
       </c>
       <c r="C276" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D276">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E276" t="s">
         <v>26</v>
       </c>
       <c r="F276" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G276" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -6885,22 +6888,22 @@
         <v>22</v>
       </c>
       <c r="B277">
-        <v>610051</v>
+        <v>610047</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D277">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E277" t="s">
         <v>26</v>
       </c>
       <c r="F277" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G277" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -6908,22 +6911,22 @@
         <v>22</v>
       </c>
       <c r="B278">
-        <v>610053</v>
+        <v>610049</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D278">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E278" t="s">
         <v>26</v>
       </c>
       <c r="F278" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G278" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -6931,22 +6934,22 @@
         <v>22</v>
       </c>
       <c r="B279">
-        <v>610055</v>
+        <v>610051</v>
       </c>
       <c r="C279" t="s">
         <v>24</v>
       </c>
       <c r="D279">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E279" t="s">
         <v>26</v>
       </c>
       <c r="F279" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G279" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -6954,22 +6957,22 @@
         <v>22</v>
       </c>
       <c r="B280">
-        <v>610057</v>
+        <v>610053</v>
       </c>
       <c r="C280" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D280">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E280" t="s">
         <v>26</v>
       </c>
       <c r="F280" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G280" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -6977,22 +6980,68 @@
         <v>22</v>
       </c>
       <c r="B281">
+        <v>610055</v>
+      </c>
+      <c r="C281" t="s">
+        <v>25</v>
+      </c>
+      <c r="D281">
+        <v>35</v>
+      </c>
+      <c r="E281" t="s">
+        <v>26</v>
+      </c>
+      <c r="F281" t="s">
+        <v>41</v>
+      </c>
+      <c r="G281" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>22</v>
+      </c>
+      <c r="B282">
+        <v>610057</v>
+      </c>
+      <c r="C282" t="s">
+        <v>24</v>
+      </c>
+      <c r="D282">
+        <v>45</v>
+      </c>
+      <c r="E282" t="s">
+        <v>26</v>
+      </c>
+      <c r="F282" t="s">
+        <v>42</v>
+      </c>
+      <c r="G282" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>22</v>
+      </c>
+      <c r="B283">
         <v>610059</v>
       </c>
-      <c r="C281" t="s">
-        <v>23</v>
-      </c>
-      <c r="D281">
+      <c r="C283" t="s">
+        <v>24</v>
+      </c>
+      <c r="D283">
         <v>55</v>
       </c>
-      <c r="E281" t="s">
-        <v>26</v>
-      </c>
-      <c r="F281" t="s">
+      <c r="E283" t="s">
+        <v>26</v>
+      </c>
+      <c r="F283" t="s">
         <v>43</v>
       </c>
-      <c r="G281" t="s">
-        <v>59</v>
+      <c r="G283" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
